--- a/光伏配储项目/电价数据/2026/蓝屋站.xlsx
+++ b/光伏配储项目/电价数据/2026/蓝屋站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33742</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7710900000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07659000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.9464900000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.96741</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17435</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27174</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25562</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24491</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8055099999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.49947</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6085700000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59062</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.75478</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.13504</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.69738</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6745</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.90455</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.54911</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.20922</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.40379</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.08424</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.0971</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31667</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.40143</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.72511</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7784</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.26017</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.81926</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.85284</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7920700000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.73645</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.49398</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.45794</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.41489</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7068300000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.61804</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.88607</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8573999999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48344</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.49754</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49009</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49049</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49005</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.52412</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.67547</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.63688</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.07645</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.73885</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.53307</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.7046699999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.10225</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.66052</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.91486</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.04423</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.30472</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18633</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.95978</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.29999</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16872</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.36133</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.06541</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15335</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.76352</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.06415</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.02545</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8993099999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.11914</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9595199999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.89675</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.90863</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.46307</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33404</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5088</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48793</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48512</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43677</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46236</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43886</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15693</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19509</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.11536</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.89289</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7226399999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7099800000000001</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.90664</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.90344</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.9253899999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.90201</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.43579</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.8135599999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.81989</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.83229</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.04406</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.57992</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.64639</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9018999999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8829600000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.73763</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.79274</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.55148</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.9446</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.53603</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51485</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52925</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.6376499999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.68509</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6694500000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6583600000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.6084</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6629700000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70111</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.48613</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5150800000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6575800000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.85499</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7929299999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.04339</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47592</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.65347</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47989</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5883200000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.71653</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.89888</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.62966</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.08499</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.81857</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.63554</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.57269</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7114</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45319</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.47548</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34151</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.50014</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.48091</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42564</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.52062</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7443200000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47655</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46314</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.75114</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.74959</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.60642</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.48228</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.44001</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.5637799999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.62175</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.87293</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.63558</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.6262799999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.5193099999999999</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.55076</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.64842</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.79777</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.57605</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66192</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.61476</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.58635</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.5145299999999999</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.48477</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.47087</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.46039</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.37188</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28867</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14325</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26783</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24202</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10724</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28915</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03212</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31639</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23584</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.2429</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.25491</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18803</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.17904</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24615</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.19128</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24622</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21193</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18953</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17052</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24696</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26863</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19777</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09648000000000001</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03972</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20599</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04916</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1941</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.008490000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06014</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05834</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31529</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.42425</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4434</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48205</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7878200000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87029</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65171</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5714400000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44679</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46065</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5809299999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.62919</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.93937</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.53808</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4362</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.42892</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.71453</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9542</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26502</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7247899999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.5709099999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26078</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26001</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28815</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32282</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.83657</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.52151</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.56726</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.46528</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.22872</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.50662</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.57353</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.44562</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.56957</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.46564</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.46344</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.46684</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.49737</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.5304099999999999</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.33885</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19436</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48602</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.64799</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.84829</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.86866</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.51066</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.55783</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41321</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5467799999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22437</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16835</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.00827</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.39382</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.46669</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.53323</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3057</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.19294</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18377</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.20379</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18104</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.17186</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.22477</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.21962</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.27113</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18245</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.25662</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.20254</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.17828</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.19816</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.2079</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.24491</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26821</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24683</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27965</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25721</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30275</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28554</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.08722</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.66411</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.49127</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48693</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43889</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43116</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5555099999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.43994</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.76374</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.5588200000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.45786</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5432400000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43631</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45242</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.50013</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.43523</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.57176</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.83999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47651</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.55669</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.5458</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.78206</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49862</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.26211</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27827</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19471</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18712</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27288</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18888</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18626</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14912</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23293</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18599</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19174</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19827</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16183</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15344</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.22804</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.24599</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.25766</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.21653</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23129</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31972</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.02668</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27194</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.59797</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.52088</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.2954</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28168</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49393</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.62799</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5891799999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6354099999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7814099999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31301</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28426</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44764</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47871</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5184099999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43025</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.69973</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8456900000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48842</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.6994</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31179</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40373</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26107</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.01298</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27304</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27272</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.46137</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.47244</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.49436</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.55164</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44055</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.43339</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.27155</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.25914</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.29323</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.21201</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.2441</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22427</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16155</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01697</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.01636</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.02829</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19582</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16059</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01662</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15584</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19177</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15355</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15884</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01697</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16148</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01707</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17209</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17792</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14411</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.14798</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.18175</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00073</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24713</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21475</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24135</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.20006</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.20599</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.19185</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.20622</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.29269</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22598</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03214</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18029</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17739</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02855</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19715</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21881</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21023</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.01853</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.04072</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.0263</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.02631</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.02656</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.02656</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.02641</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19174</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.02656</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.02655</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16966</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.0407</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.02572</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.02223</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24318</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01714</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.008400000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.21376</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00678</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.01731</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02734</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.03251</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03141</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.23734</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.02575</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26562</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.01101</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27681</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16083</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.15621</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16045</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15793</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15412</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.02261</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.02152</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.01972</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18394</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22841</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8565199999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8624700000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08915000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.02514</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24544</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.55332</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00185</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06939000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4754</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.63164</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5081100000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7539600000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9029299999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.58551</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.77054</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.76877</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7725599999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.86112</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41452</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30463</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45586</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25831</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18184</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24284</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.2094</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.24641</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19551</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.15886</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19121</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15357</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.15616</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.14764</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17307</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22453</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24316</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24889</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28315</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25868</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28837</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5576599999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42278</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45369</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41789</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46219</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.17947</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.77447</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.77884</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41768</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5240900000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.65306</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81616</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5302</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42281</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31418</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.48762</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.49573</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.9807100000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.76897</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5277000000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.66326</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.45962</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54079</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49215</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6392899999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6019800000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.92583</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.78427</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6804199999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5678</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3188</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28278</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26442</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.54199</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19836</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5099900000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.45736</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.61738</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.5925900000000001</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.65174</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.5116700000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.52646</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45536</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32261</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6769400000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.44363</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.45876</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.7063700000000001</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.73161</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.52832</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.61373</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.7792100000000001</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.54592</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.49039</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40329</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33684</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.47557</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17612</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14578</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19869</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14675</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12182</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22637</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14334</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18751</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.18682</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.19949</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.22665</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.19137</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.66455</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.75666</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.5372</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.2278</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.5849099999999999</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.64515</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.44321</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.7225499999999999</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.59013</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.7297899999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.06124</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.77401</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.43114</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.71036</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.43081</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.67975</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.70823</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.60682</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.44035</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36702</v>
       </c>
     </row>
   </sheetData>
